--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogisticsError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogisticsError.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
-    <sheet name="费用信息" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
       <rPr>
@@ -140,81 +139,6 @@
   <si>
     <t>{.errorMsg}</t>
   </si>
-  <si>
-    <t>来源单号</t>
-  </si>
-  <si>
-    <t>物流运单号</t>
-  </si>
-  <si>
-    <t>业务单号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>费用名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>预估费用金额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>币种</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -236,12 +160,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -396,6 +314,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -734,137 +658,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,9 +796,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1198,22 +1119,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1248,47 +1169,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="5" width="16.0916666666667" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogisticsError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogisticsError.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,38 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>订单号</t>
+  </si>
+  <si>
+    <t>出库单号</t>
+  </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>订单号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -68,7 +45,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>出库单号</t>
+      <t>物流跟踪号</t>
     </r>
   </si>
   <si>
@@ -128,6 +105,9 @@
     <t>{.outstockCode}</t>
   </si>
   <si>
+    <t>{.trackNo}</t>
+  </si>
+  <si>
     <t>{.trackStatusName}</t>
   </si>
   <si>
@@ -160,14 +140,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -314,12 +300,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -658,137 +638,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -796,6 +776,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,58 +1092,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="3" width="13.3666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="5" width="32.375" customWidth="1"/>
-    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="1" max="4" width="13.3666666666667" customWidth="1"/>
+    <col min="5" max="5" width="21.25" customWidth="1"/>
+    <col min="6" max="6" width="32.375" customWidth="1"/>
+    <col min="7" max="7" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576">
       <formula1>40544</formula1>
       <formula2>47849</formula2>
     </dataValidation>
